--- a/artfynd/A 55799-2024 artfynd.xlsx
+++ b/artfynd/A 55799-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>2372133</v>
       </c>
       <c r="B2" t="n">
-        <v>104838</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>107908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520772.0271264882</v>
+        <v>520772</v>
       </c>
       <c r="R2" t="n">
-        <v>6310242.788361628</v>
+        <v>6310243</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,19 +757,9 @@
           <t>2012-06-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-06-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
